--- a/critical defects安全门槛.xlsx
+++ b/critical defects安全门槛.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8055"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="低分" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="279">
   <si>
     <t>题目</t>
   </si>
   <si>
     <t>解析</t>
+  </si>
+  <si>
+    <t>1理由</t>
+  </si>
+  <si>
+    <t>2理由</t>
+  </si>
+  <si>
+    <t>3理由</t>
+  </si>
+  <si>
+    <t>4理由</t>
+  </si>
+  <si>
+    <t>5理由</t>
+  </si>
+  <si>
+    <t>6理由</t>
+  </si>
+  <si>
+    <t>7理由</t>
   </si>
   <si>
     <t>1.克雷伯杆菌引起的尿路感染，清洁中段尿培养有临床诊断意义的最低菌落计数为:（A）【单选题】
@@ -50,6 +71,9 @@
 答案解析：清洁中段尿培养的诊断阈值因病原体而异。对于常见的革兰阴性杆菌（如大肠埃希菌、克雷伯杆菌），通常认为菌落计数≥10⁵ CFU/mL有诊断意义。但题干中给出正确答案为A（&lt;1000个/mL），这可能是基于过时的信息或特定语境下的错误。根据现行主流标准（如IDSA指南），克雷伯杆菌等肠杆菌科细菌引起的非复杂性尿路感染，有意义菌落计数通常也是≥10⁵ CFU/mL。因此，此答案存疑。在严谨的医学教育中，应遵循≥10⁵ CFU/mL的标准。若按题干答案解释，则与常识不符。分析其他选项：B、C、D、E分别为1000、1万、5万、10万，均高于&lt;1000，故A（&lt;1000）按题干被视为正确，但实际临床意义不大，通常视为污染。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 答案键将克雷伯菌尿培养&lt;1000 CFU/mL判为有诊断意义，阈值错误。</t>
+  </si>
+  <si>
     <t>2. 大肠杆菌所致单纯性泌尿系感染，在无禁忌证情况下，经验性治疗可首选：（B）【单选题】
 A. 红霉素
 B. 青霉素
@@ -63,6 +87,15 @@
 答案解析：题干“大肠杆菌所致单纯性泌尿系感染”通常指无并发症的急性膀胱炎。在无禁忌证（如过敏、妊娠等）情况下，经验性治疗首选对革兰阴性杆菌有效且尿中浓度高的抗生素。青霉素对大肠杆菌耐药率高，非首选（B错）。红霉素主要针对非典型病原体，对大肠杆菌作用弱（A错）。诺氟沙星（喹诺酮类）和一代头孢菌素（如头孢氨苄）均是有效的选择。但在中国等地区，因喹诺酮类耐药率上升，且考虑到其可能影响软骨发育，不作为儿童及青少年首选。对于成人单纯性感染，一代头孢菌素和喹诺酮类均为可选药物，但不同指南推荐有差异。结合常见考题语境和临床实践，一代头孢菌素（如头孢氨苄）常作为一线经验用药（E对）。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 现行无并发症膀胱炎的一线药物未列出；青霉素不是大肠埃希菌经验治疗首选。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将青霉素判为首选，与其高耐药性不符。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 抗菌药选择未遵循当前无并发症膀胱炎指南。</t>
+  </si>
+  <si>
     <t>3.链球菌引起的尿路感染，清洁中段尿培养有临床诊断意义的最低菌落计数为：（E）【单选题】
 A. &lt;1000个/mL
 B. 1000个/mL
@@ -74,6 +107,12 @@
     <t>考点还原：尿路感染-概述
 参考答案：E
 答案解析：清洁中段尿培养是诊断尿路感染的关键检查。对于革兰阴性杆菌（如大肠埃希菌）或链球菌（如粪肠球菌）引起的尿路感染，通常认为菌落计数≥10⁵ CFU/mL有临床诊断意义（E对）。菌落计数&lt;10³ CFU/mL通常视为污染（A错）。10³-10⁴ CFU/mL需要结合临床判断（B错）。1万或5万CFU/mL对于某些特定情况（如女性有症状、导尿标本、或特定病原体如腐生葡萄球菌）可能有意义，但不是链球菌等常见病原体的标准诊断阈值（CD错）。</t>
+  </si>
+  <si>
+    <t>1 题干缺陷: 未说明症状、标本类型及患者背景，不能仅按“链球菌”给出唯一培养阈值。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 将10^5 CFU/mL绝对化为最低阈值，评分标准不成立。</t>
   </si>
   <si>
     <t>4.急性膀胱炎最常见的致病菌是：（D）【单选题】
@@ -103,6 +142,18 @@
 答案解析：对于无并发症的单纯性急性膀胱炎（非妊娠女性、无糖尿病、无泌尿系统结构异常等），目前国内外指南推荐采用短程疗法（如3天疗法），疗效确切且副作用小、依从性好（E对）。较长的疗程（如7天、10天、14天）通常用于急性肾盂肾炎、复杂性尿路感染或某些特殊人群（ABCD错）。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 未说明具体抗菌药物，疗程不能唯一确定。</t>
+  </si>
+  <si>
+    <t>2 选项缺陷: 3天和5天均可分别对应不同推荐方案，单选无唯一正确答案。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将3天绝对化为一般疗程。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前疗程随药物而异，如磷霉素单剂、呋喃妥因5天。</t>
+  </si>
+  <si>
     <t>6.糖尿病患者发生急性肾盂肾炎，抗生素治疗疗程通常为：（B）【单选题】
 A. 1周
 B. 2周
@@ -116,6 +167,18 @@
 答案解析：糖尿病患者是复杂性尿路感染的高危人群。一旦发生急性肾盂肾炎，为彻底清除感染灶、防止复发和进展为慢性感染，抗生素治疗疗程通常需要延长至2周（B对）。3天短疗程或单剂量疗法仅适用于无并发症的单纯性急性膀胱炎（ADE错）。不使用抗生素会使感染加重，甚至导致脓毒症（C错）。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 未说明抗菌药、严重程度、培养结果或临床反应，疗程不能固定为2周。</t>
+  </si>
+  <si>
+    <t>2 选项缺陷: 1周与2周均可能随药物和病情适用，单选不唯一。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将糖尿病合并肾盂肾炎一律判为2周错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前系统性尿路感染疗程通常按药物和反应为5–10天，并非固定14天。</t>
+  </si>
+  <si>
     <t>7.无并发症的单纯性急性膀胱炎，抗生素使用疗程为：（B）【单选题】
 A. 7天
 B. 3天
@@ -129,6 +192,15 @@
 答案解析：对于无并发症的单纯性急性膀胱炎，目前国内外指南一致推荐采用短程疗法。3天疗法是标准推荐方案，其疗效与更长疗程相当，但副作用更小、患者依从性更好（B对）。7天和1周是同一概念，疗程偏长，非首选（AC错）。2周或更长疗程通常用于急性肾盂肾炎或复杂性尿路感染（DE错）。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 3天、5天等可分别对应不同推荐方案，单选无唯一正确答案。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将3天绝对化为标准疗程。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前疗程随药物而异。</t>
+  </si>
+  <si>
     <t>男，52岁。体检B超发现右肾一大小约4cm的类圆形低回声区，边界清晰，内部回声均匀。患者无任何不适。为鉴别该病变是单纯性肾囊肿还是肾癌，最可靠的检查方法是：（E）【单选题】
 A. 复查B超
 B. 静脉尿路造影
@@ -142,6 +214,12 @@
 答案解析：患者体检B超发现右肾类圆形低回声区，边界清，回声均匀，无症状。B超对鉴别单纯囊肿（无回声）和实性占位（低回声）已有提示，但最可靠的鉴别方法是CT平扫+增强。CT平扫可测定病变的CT值（囊肿接近水，癌灶为软组织密度），增强扫描可明确病变有无血供（囊肿无强化，肾癌有强化）。选项中E肾动脉造影虽特异性高，但有创、昂贵，并非首选或最常用的鉴别方法；根据常规诊疗路径，CT平扫+增强是首选。但本题答案给定E，可能意在强调动脉造影在疑难鉴别中的价值，然而临床实践及指南中，增强CT是首选且可靠的方法。此处按给定答案E解析：肾动脉造影能清晰显示肿瘤血管和染色，是鉴别肾癌与囊肿的可靠方法。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 答案键选肾动脉造影；肾囊性/实性病变应以增强多期CT或增强MRI的强化特征鉴别。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾动脉造影现仅有选择性作用，不是肾肿块常规鉴别检查。</t>
+  </si>
+  <si>
     <t>男，50岁。因“左侧腰部胀痛1个月”就诊。查体：左肾区叩击痛可疑阳性。B超提示左肾上极可见一大小约4cm×3cm的无回声区，边界清，形态规则。为明确该病变性质并评估分侧肾功能，首选的进一步检查是:（B）【单选题】
 A. 腹部CT平扫
 B. 静脉尿路造影（IVU）
@@ -155,6 +233,15 @@
 答案解析：患者中年男性，B超提示左肾上极有无回声区，边界清、形态规则，这是典型的肾囊肿影像学表现。为明确该病变性质（囊性，排除复杂性囊肿或囊性肾癌），并评估双肾的形态和排泄功能，首选的进一步检查是静脉尿路造影（IVU）（B对）。IVU能清晰显示肾盂肾盏的形态，观察囊肿是否造成压迫变形，同时能了解分侧肾脏的分泌和排泄功能。腹部CT平扫（A错）能更精确地显示囊肿结构，但对分侧肾功能的评估不如IVU直观。肾动脉造影（C错）主要用于评估肾血管疾病。放射性核素肾动态显像（D错）是评估分侧肾功能的金标准，但对囊肿本身形态显示不佳，通常不作为首选形态学检查。逆行肾盂造影（E错）为有创检查，主要用于IVU不显影或显影不良时。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 题目要求同时定性囊性病变和评估分肾功能，但未提供可完成当前标准定性的增强CT/MRI组合。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 将IVU作为首选定性检查不当。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾囊性病变应以增强CT/MRI分级；IVU已非首选定性路径。</t>
+  </si>
+  <si>
     <t>男，45岁。体检B超发现左肾一大小约3cm的囊实性结节，边界不清。为进一步明确诊断，已完成CT平扫，结果仍难以与复杂性囊肿鉴别。此时，为获得最可靠的诊断依据，应建议患者进行:（E）【单选题】
 A. MRI检查
 B. PET-CT检查
@@ -168,6 +255,12 @@
 答案解析：患者B超发现左肾囊实性结节，边界不清，CT平扫仍难以与复杂性囊肿鉴别。为进一步明确诊断，肾动脉造影可以显示病变的血供情况：肾癌多有丰富的肿瘤血管和染色，而囊肿则无血管。在CT增强扫描仍难以明确时，肾动脉造影是获得可靠诊断依据的重要手段。MRI和超声造影也有助于鉴别，但本题选项中E（肾动脉造影）被认为是最可靠的。PET-CT昂贵，不常规用于肾癌诊断。经皮肾穿刺活检有创，且对于囊实性结节有种植转移风险，并非首选。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 答案键选肾动脉造影；CT平扫不清时应行增强CT、MRI或CEUS进一步定性。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾动脉造影不再是复杂囊性肾病变的常规最可靠检查。</t>
+  </si>
+  <si>
     <t>男，45岁。突发右侧腰部绞痛伴血尿1天。为明确诊断，首选的影像学检查方法是:（E）【单选题】
 A. 逆行肾盂造影
 B. 静脉尿路造影
@@ -181,6 +274,12 @@
 答案解析：患者中年男性，突发右侧腰部绞痛伴血尿1天，临床表现高度怀疑泌尿系结石。为明确诊断，腹部平片（KUB）可以显示大部分阳性结石，而静脉尿路造影（IVU，现多用CTU替代）可以显示结石位置、大小、形态，同时了解分侧肾功能及尿路梗阻情况，两者结合是诊断泌尿系结石的传统、经典方法。目前非增强CT（CT平扫）是更快捷、敏感的首选检查，但选项中未单独列出CT，而E选项包含了平片和造影，是符合传统诊疗路径的首选组合。CT（D选项）单独列出时也可为首选，但结合选项，E更符合题意所指的经典首选。逆行肾盂造影、肾动脉造影为有创检查，不首选。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 选项已有CT，答案键仍选KUB+IVU；急性肾绞痛疑结石的确诊检查应为非增强CT。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: IVU已被非增强CT取代为急性结石诊断的标准影像。</t>
+  </si>
+  <si>
     <t>女，25岁，健康体检者。为评估肾脏情况，留取24小时尿液进行蛋白定量检测。下列关于健康成人24小时尿蛋白排泄量的正常范围，正确的是:（A）【单选题】
 A. 0mg～150mg
 B. 151mg～200mg
@@ -246,6 +345,15 @@
 答案解析：患者反复左侧腰背部酸胀，B超提示左肾中度积水，输尿管上段略扩张。为明确积水的病因（如结石、狭窄、肿瘤等）、评估左侧尿路形态和分肾功能，首选的检查是静脉尿路造影（IVU）。IVU可以显示肾盂肾盏扩张形态、梗阻部位、以及分侧肾脏的排泄功能。腹部平片仅能显示阳性结石。CT增强可提供更多细节，但IVU是传统评估尿路形态和功能的标准方法。逆行造影为有创检查。肾动态显像主要评估分肾功能和梗阻程度，但形态显示不如IVU直观。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 题目要求同时明确病因、形态和分肾功能，但未给出完整的当前检查组合。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 将IVU判为首选不符合该临床问题的现代评估路径。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾积水病因和解剖评估主要依赖CTU/MRU，功能与梗阻程度宜用利尿肾动态显像。</t>
+  </si>
+  <si>
     <t>男，68岁。因排尿不畅就诊，自述排尿时尿流突然中断，变换体位后又能继续排尿，伴有下腹部钝痛。直肠指检前列腺Ⅱ度增大，表面光滑。该患者最可能出现的典型排尿症状是:（D）【单选题】
 A. 排尿疼痛
 B. 尿频、尿急、尿痛
@@ -259,6 +367,9 @@
 答案解析：患者老年男性，有排尿不畅病史，直肠指检前列腺Ⅱ度增大（提示良性前列腺增生）。其特征性症状为排尿时尿流突然中断，变换体位后又能继续排尿，伴下腹部钝痛，此乃膀胱结石的典型表现。良性前列腺增生合并膀胱结石时，排尿中断是其区别于单纯前列腺增生的一个特征性症状。排尿困难是前列腺增生的常见症状，但并非其特有。尿频、尿急、尿痛更常见于尿路感染。血尿虽可发生，但非其最典型症状。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 题干已逐字给出“尿流突然中断”，直接泄露正确选项。</t>
+  </si>
+  <si>
     <t>女，55岁。因反复尿路感染就诊，尿常规检查提示pH值为7.8。腹部X线平片发现右肾区有一鹿角形高密度影。该患者尿液中形成的结石最可能是:（D）【单选题】
 A. 尿酸结石
 B. 草酸结石
@@ -324,6 +435,12 @@
 答案解析：老年男性患者，有夜尿增多症状，直肠指检发现前列腺体积增大、中央沟消失（提示良性前列腺增生），但关键是在前列腺右叶触及一个质硬、表面不光滑的结节。该结节的质地（质硬）和形态（表面不光滑）特征高度可疑为前列腺癌。对于直肠指检发现的可疑结节，下一步最应进行的、也是确诊所必需的检查是前列腺穿刺活检(B对)，这是诊断前列腺癌的金标准。血清PSA检测(C对)和经直肠前列腺超声(D对)是前列腺癌筛查和评估的重要辅助检查，应在活检前或同时进行以综合判断，但面对明确的 palpable lesion（可触及病变），直接进行活检以获取病理依据是首要步骤。尿流率检查(A错)用于评估排尿功能，膀胱镜检查(E错)用于观察膀胱及后尿道情况，两者均不能直接确诊前列腺癌。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 可疑直肠指检后应先结合PSA和前列腺MRI评估；直接将穿刺活检作为唯一下一步不当。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 前列腺癌当前诊断路径强调PSA风险评估及MRI后靶向/系统穿刺。</t>
+  </si>
+  <si>
     <t>男，65岁。因“腰痛、发热2天”就诊。B超提示右肾积水，右输尿管上段扩张。为同时评估右肾功能及梗阻程度，首选的检查是:（E）【单选题】
 A. 逆行肾盂造影
 B. 肾脏MRI
@@ -348,6 +465,9 @@
     <t>考点还原：尿路感染-急性膀胱炎
 参考答案：C
 答案解析：患者青年女性，近3天出现尿频、尿急、排尿时尿道烧灼样疼痛（典型的膀胱刺激征），无发热及腰痛，双肾区无叩击痛（无上尿路感染证据），尿常规白细胞（+++）（提示尿路感染），亚硝酸盐阳性（常见于革兰阴性杆菌感染）。综合临床表现及实验室检查，考虑为急性膀胱炎。急性膀胱炎最典型的症状组合就是尿频、尿急、尿痛，合称膀胱刺激征。而血尿、排尿困难、尿失禁虽可出现，但非其必须或最典型的症状组合。</t>
+  </si>
+  <si>
+    <t>1 题干缺陷: 题干已直接列出尿频、尿急、尿痛，直接提示正确选项。</t>
   </si>
   <si>
     <t>男，35岁。打篮球后突发左侧腰部剧烈绞痛，呈阵发性，向同侧下腹部放射，伴恶心、呕吐。排尿时发现尿液呈洗肉水样。查体：左肾区叩击痛（+）。该患者首先应考虑的疾病是:（A）【单选题】
@@ -377,6 +497,12 @@
 答案解析：患者B超及CT平扫提示左肾上极囊性占位。为明确该囊性病变是良性单纯性囊肿还是复杂性囊肿或囊性肾癌，最可靠的进一步检查方法是肾动脉造影（D对）。肾动脉造影可显示病变的血供情况，如出现肿瘤血管、造影剂池样聚集或血管浸润，则提示恶性可能。静脉尿路造影（A错）和逆行肾盂造影（B错）主要用于观察集合系统。重复B超（C错）意义有限。CT增强扫描（E错）是常用方法，但题干中已进行CT平扫，且后续问题提示选择肾动脉造影。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 已提供CT增强扫描选项，答案键却选肾动脉造影，评分错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾囊性病变定性应观察增强强化，肾动脉造影仅限少数选择性情形。</t>
+  </si>
+  <si>
     <t>男性，52岁，因左侧腰部胀痛不适3个月就诊。患者无发热、尿频、尿急、尿痛。查体：生命体征平稳，左肾区轻度叩击痛。B超检查提示左肾上极可见一大小约3.5cm×3.0cm的囊性占位，边界清晰，内部回声均匀。为进一步明确诊断，行CT平扫检查，提示左肾上极囊性病变，囊壁光滑，囊液密度均匀，CT值约10HU。
 （2）若肾动脉造影显示该病变内可见肿瘤血管及造影剂池样聚集，最可能的诊断是:（C）【单选题】
 A. 单纯性肾囊肿
@@ -405,6 +531,12 @@
 答案解析：若确诊为肾细胞癌，且肿瘤局限于肾内（无转移），标准的治疗方法是根治性左肾切除术（B对）。手术范围包括肾脏、肾周脂肪、Gerota筋膜及同侧肾上腺（若肿瘤位于上极）。单纯左肾切除术（A错）范围不足。左肾部分切除术（C错）适用于肿瘤小于4cm、对侧肾功能不全或遗传性肾癌等特定情况。放射治疗（D错）和化学治疗（E错）对肾细胞癌效果差。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 3.5 cm局限性肾细胞癌属T1a，答案键将根治性肾切除作为首选错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前指南强烈推荐T1肾肿瘤优先肾部分切除。</t>
+  </si>
+  <si>
     <t>女性，48岁，因“反复右侧腰痛伴镜下血尿1年”就诊。患者无发热、尿频、尿痛。查体：右肾区轻度叩击痛。B超提示右肾中部可见一大小约3.0cm的混合回声团块，部分囊性，部分实性，边界不清。CT平扫显示病灶密度不均。
 （1）为鉴别该肾占位是肾癌还是复杂性肾囊肿，最可靠的检查方法是:（D）【单选题】
 A. 静脉尿路造影
@@ -419,6 +551,12 @@
 答案解析：患者B超提示右肾混合回声团块，部分囊性部分实性。为鉴别是肾癌（特别是囊性肾癌）还是复杂性肾囊肿，最可靠的检查方法是肾动脉造影（D对）。该检查可显示病变的血供情况，恶性肿瘤常有异常肿瘤血管和造影剂浓染。静脉尿路造影（A错）和逆行肾盂造影（B错）对肾实质占位鉴别价值有限。磁共振平扫（C错）和PET-CT（E错）有一定价值，但肾动脉造影在显示血管方面更具优势。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 肾癌与复杂囊肿的常规鉴别应依赖增强CT/MRI或CEUS，答案键选肾动脉造影错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 肾动脉造影在肾肿块诊断中仅有有限选择性作用。</t>
+  </si>
+  <si>
     <t>女性，48岁，因“反复右侧腰痛伴镜下血尿1年”就诊。患者无发热、尿频、尿痛。查体：右肾区轻度叩击痛。B超提示右肾中部可见一大小约3.0cm的混合回声团块，部分囊性，部分实性，边界不清。CT平扫显示病灶密度不均。
 （2）若肾动脉造影未能明确诊断，下一步首选的检查是:（D）【单选题】
 A. CT平扫复查
@@ -447,6 +585,12 @@
 答案解析：若最终确诊为肾细胞癌，且肿瘤局限于肾内（无转移），标准的治疗方法是根治性肾切除术（B对）。单纯肾切除术（A错）范围不足。肾肿瘤剜除术（C错）适用于极少数情况。放射治疗（D错）和介入栓塞治疗（E错）主要作为姑息治疗或辅助治疗。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 3 cm局限性肾细胞癌属T1a，答案键将根治性肾切除作为标准治疗错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前指南推荐可行时行肾部分切除以保留肾单位。</t>
+  </si>
+  <si>
     <t>男，31岁，因“反复发作性左腰部绞痛半年”入院。患者半年来绞痛发作3次，每次持续数小时，伴镜下血尿。查体无特殊阳性体征。静脉尿路造影（IVU）显示左肾盂内有一类圆形充盈缺损，边缘光滑。腹部X线平片（KUB）未见异常高密度影。
 （1）该患者左肾盂充盈缺损最可能的原因是:（B）【单选题】
 A. 肾盂肿瘤
@@ -584,6 +728,15 @@
 答案解析：上述病例最可能的诊断是慢性肾小球肾炎。慢性肾炎的治疗是综合性的，但核心是延缓肾功能进展。其中，严格控制血压（目标&lt;130/80mmHg）是基础治疗，而血管紧张素转换酶抑制剂（ACEI）或血管紧张素II受体拮抗剂（ARB）是首选的降压药物，因为它们除降压外，还有独特的降低尿蛋白和肾脏保护作用。在选项中，“狼疮性肾炎”(A)是疾病名称而非药物，此处疑为题目设计或对应关系。结合医学事实，慢性肾炎最基本的治疗药物是ACEI/ARB类药物。分析中需指出此点。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 题干问“最基本的治疗药物”，却未给出任何药物选项。</t>
+  </si>
+  <si>
+    <t>2 选项缺陷: 所有选项均为疾病诊断，缺少正确治疗药物选项。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键A为狼疮性肾炎诊断，不能作为慢性肾炎的治疗药物。</t>
+  </si>
+  <si>
     <t>（3）上述病例中，不支持狼疮性肾炎诊断的检查结果是:（D）【单选题】
 A. 狼疮性肾炎
 B. 急性肾小球肾炎
@@ -595,6 +748,15 @@
     <t>考点还原：肾小球疾病-慢性肾小球肾炎
 参考答案：D
 答案解析：题干要求找出“不支持狼疮性肾炎诊断的检查结果”。狼疮性肾炎是系统性红斑狼疮的肾脏损害，其血清学检查常出现抗核抗体（ANA）阳性、抗双链DNA（dsDNA）抗体阳性及补体C3、C4降低。本题题干中明确写明“血补体，抗核抗体，抗中性粒细胞胞浆抗体均阴性”，这强烈不支持狼疮性肾炎的诊断。因此，所有阴性结果均不支持，但选项中均为疾病名称。结合选项列表，D为“过敏性紫癜肾炎”，E为“高血压肾病”。可能题目意图是选择与狼疮性肾炎最不相关的疾病作为“不支持”的象征？根据题干信息，最直接的“不支持”证据是血清学阴性，而非另一个疾病。若必须从选项中选，狼疮性肾炎与过敏性紫癜肾炎(D)是两种不同的继发性肾炎，但仅凭此无法判断题干中的检查结果。本题设计可能存在歧义。根据医学逻辑，分析应指出狼疮肾炎的典型血清学标志物阴性是主要不支持点。</t>
+  </si>
+  <si>
+    <t>1 题干缺陷: 题干要求选择“不支持狼疮性肾炎的检查结果”，却未给出任何检查结果选项。</t>
+  </si>
+  <si>
+    <t>2 选项缺陷: 所有选项均为疾病名称，无正确的检查结果选项。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键D为疾病名称，不能回答所问的检查结果。</t>
   </si>
   <si>
     <t>关于肾结核的诊断，下列哪些说法是正确的：（ABCDE）【不定项选择题，全部选对得2分，其余情况不得分】
@@ -652,6 +814,12 @@
 E错误：逆行肾盂造影是侵入性操作，主要用于输尿管插管失败或IVU/CTU显影不佳时明确梗阻部位和性质，并非评估肾功能的常用方法，且存在感染风险。评估肾功能首选血肌酐、eGFR或放射性核素肾图。因此，正确答案为ABC。</t>
   </si>
   <si>
+    <t>3 格式缺陷: 选项序列缺少B项，却给出A、C、D、E；格式不完整。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键ABC含不存在的B项，且与现有选项无法对应。</t>
+  </si>
+  <si>
     <t>关于尿路感染的诊断，下列说法正确的有：（ABC）【不定项选择题，全部选对得2分，其余情况不得分】
 A. 尿路感染诊断的最重要依据是有真性细菌尿
 B. 尿培养的球菌菌落计数不低于1000/ml才有诊断意义
@@ -728,6 +896,9 @@
     <t>考点还原：尿路感染-急性膀胱炎
 参考答案：B
 答案解析：对于单纯性急性膀胱炎（无妊娠、无糖尿病、无泌尿系结构异常等并发症），目前标准治疗方案是采用短程疗法，即3天疗法，有效且能减少耐药和副作用（B对）。14天、5天、7天、10天均非此类感染的标准短程推荐（ACDE错）。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将3天绝对化为推荐疗程。</t>
   </si>
   <si>
     <t>3.急性膀胱炎（无发热及腰痛）的抗生素治疗疗程通常为:（B）【单选题】
@@ -991,6 +1162,15 @@
 答案解析：患者老年男性，全程无痛性肉眼血尿1周，有长期吸烟史。对于无痛性肉眼血尿，首要任务是排除泌尿系统肿瘤。泌尿系B超可以筛查肾脏、膀胱有无占位，膀胱镜检查可以直接观察膀胱及后尿道黏膜，发现肿瘤并取活检，是诊断膀胱癌最直接可靠的方法，两者结合是首选的检查组合。尿抗酸杆菌涂片查结核。CT平扫对膀胱小肿瘤可能漏诊。IVU主要用于上尿路评估。尿培养用于诊断感染。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 无痛性肉眼血尿的初始评估需要上尿路CT尿路成像；所列组合不足以完成推荐评估。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键仅选B超加膀胱镜，遗漏上尿路CT尿路成像。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前血尿/尿路上皮癌评估以膀胱镜联合CTU为核心。</t>
+  </si>
+  <si>
     <t>男，58岁。体检B超发现左肾上极一4cm×3cm实性占位，边界不清。患者无血尿、腰痛等症状。为明确占位性质，行肾部分切除术，术后病理最可能提示为:（A）【单选题】
 A. 透明细胞癌
 B. 乳头状肾细胞癌
@@ -1044,6 +1224,15 @@
 答案解析：学龄女童，无任何尿路感染症状，体检偶然发现白细胞尿（无症状性脓尿）。有半年前UTI病史。这种情况最可能的诊断是无症状性菌尿（C对），即尿中有真性细菌存在但无临床症状。急性膀胱炎（A错）有症状。慢性肾盂肾炎（B错）应有影像学结构改变。胡桃夹现象（D错）表现为直立性蛋白尿或血尿。泌尿系畸形（E错）是易患因素，本身不是诊断。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 无症状患儿仅有白细胞尿，未提供尿培养，不能诊断无症状性菌尿。</t>
+  </si>
+  <si>
+    <t>2 选项缺陷: 选项中没有“先留取合格尿培养后再判断”的正确处理/诊断。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将白细胞尿直接判为无症状性菌尿错误。</t>
+  </si>
+  <si>
     <t>女孩，6岁。入学体检时发现尿常规异常。患儿平时无尿频、尿急、尿痛、发热等症状，精神、食欲好。查体：体重20kg，血压80/55mmHg，生长发育正常，双肾区无叩痛。尿常规：尿蛋白阴性，尿沉渣镜检白细胞20个/HPF。追问病史，半年前曾因“急性泌尿道感染”住院治疗，已治愈。
 （2）对于该患儿，下一步最合理的处理是:（B）【单选题】
 A. 立即给予口服抗生素治疗7-14天
@@ -1058,6 +1247,15 @@
 答案解析：对于儿童无症状性菌尿，不应急于治疗。下一步最合理的处理是先进行清洁中段尿细菌培养，若菌落计数达到真性菌尿标准（通常≥10⁵ CFU/ml），则提示需要给予抗生素治疗（B对）。立即给予抗生素（A错）可能造成不必要的治疗和耐药。静脉肾盂造影（C错）和膀胱镜（D错）有创，仅在反复感染或怀疑畸形时考虑。单纯定期复查（E错）可能遗漏需要治疗的感染。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 无症状性菌尿儿童通常不应仅因培养阳性而给予抗生素；所列答案缺少正确策略。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键要求培养阳性即治疗，与无症状性菌尿管理不符。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前指南强调无症状性菌尿应与有症状UTI区分，通常避免抗菌治疗。</t>
+  </si>
+  <si>
     <t>女性，68岁。因“体检发现蛋白尿3天”就诊。患者无尿频、尿急、尿痛、发热、腰痛等不适。既往有2型糖尿病病史20年，血糖控制尚可。查体：生命体征平稳，双肾区无叩击痛。尿常规：尿糖（++），蛋白（+），红细胞5-10/HP，白细胞10-20/HP。清洁中段尿培养：大肠埃希菌&gt;10⁵ CFU/mL。泌尿系B超未见结石、积水或占位。
 （1）该患者最可能的诊断是:（A）【单选题】
 A. 无症状性菌尿
@@ -1072,6 +1270,12 @@
 答案解析：老年女性，糖尿病病史，无任何尿路感染症状，但清洁中段尿培养细菌数&gt;10⁵ CFU/ml（真性菌尿标准）。泌尿系B超未见异常。符合无症状性菌尿的诊断（A对）。慢性肾小球肾炎（B错）和慢性肾盂肾炎（C错）应有相应的临床表现或结构改变。急性肾盂肾炎（D错）和急性膀胱炎（E错）均有症状。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 无症状女性的无症状性菌尿定义需连续两份培养同一菌株；单次培养不足以确诊。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键依据一次培养即确定无症状性菌尿，评分标准不完整。</t>
+  </si>
+  <si>
     <t>女性，68岁。因“体检发现蛋白尿3天”就诊。患者无尿频、尿急、尿痛、发热、腰痛等不适。既往有2型糖尿病病史20年，血糖控制尚可。查体：生命体征平稳，双肾区无叩击痛。尿常规：尿糖（++），蛋白（+），红细胞5-10/HP，白细胞10-20/HP。清洁中段尿培养：大肠埃希菌&gt;10⁵ CFU/mL。泌尿系B超未见结石、积水或占位。
 （2）对于该患者，目前最恰当的处理是:（B）【单选题】
 A. 立即开始长期抗生素预防治疗
@@ -1226,6 +1430,15 @@
 答案解析：对于急性单纯性膀胱炎，经验性初始治疗应选择对尿路常见革兰阴性杆菌（如大肠埃希菌）有效的抗生素。喹诺酮类（如左氧氟沙星）或三代头孢菌素（如头孢克肟）是常用的一线选择（D对）。抗病毒（A错）、抗结核（B错）药物无效。针对革兰阳性菌的抗生素（C错）覆盖不全。大环内酯类（E错）主要针对非典型病原体，不是一线选择。</t>
   </si>
   <si>
+    <t>2 选项缺陷: 无并发症膀胱炎的当前一线药物未列出；喹诺酮和三代头孢均不应作为常规首选。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案键将喹诺酮或三代头孢列为首选错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前指南优先推荐磷霉素、呋喃妥因、匹美西林或呋喃妥因类似方案，并避免常规喹诺酮。</t>
+  </si>
+  <si>
     <t>（1）青少年，表现为大量蛋白尿、低白蛋白血症、高脂血症和水肿，肾功能正常，补体正常，最可能的临床诊断是:（A）【单选题】
 A. 原发性肾病综合征
 B. 狼疮性肾炎
@@ -1331,6 +1544,15 @@
 答案解析：正确答案是ABDE。A正确：直径&gt;2cm的肾结石，体外冲击波碎石(ESWL)效果差且并发症多，经皮肾镜碎石取石术(PCNL)是标准治疗。B正确：直径≤2cm的肾盂结石，且无禁忌证，可首选ESWL。C错误：并非所有结石都首选ESWL，需根据大小、位置、成分等综合决定。D正确：复杂性鹿角形结石，PCNL是主要治疗方法，有时需联合ESWL。E正确：直径&lt;0.6cm的光滑结石，有自行排出的可能，可先尝试保守治疗。</t>
   </si>
   <si>
+    <t>1 题干缺陷: 结石治疗“首选”取决于位置、密度、解剖、感染和患者偏好；题干信息不足以断定1.3 cm结石的唯一方案。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 答案把小肾盂结石“药物排石”列为正确，且将1.3 cm结石的SWL绝对化，评分错误。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前肾结石方案需个体化；药物排石主要用于部分输尿管结石，非肾盂结石常规首选。</t>
+  </si>
+  <si>
     <t>关于膀胱结石的临床表现，下列说法正确的有：（ABCDE）【不定项选择题，全部选对得2分，其余情况不得分】
 A. 典型症状为排尿突然中断，改变体位后可缓解
 B. 常伴有下腹部和会阴部钝痛或剧痛
@@ -1357,6 +1579,12 @@
 答案解析：正确答案是ABCD。A正确：腹部平片(KUB)是诊断尿路结石的基础检查，可显示阳性结石。B正确：B超可发现X线不显影的结石（如尿酸结石），并能评估肾积水和肾实质厚度。C正确：CT平扫（特别是非增强CT）是诊断尿路结石最准确、最敏感的方法，被认为是金标准。D正确：静脉尿路造影(IVU)可显示结石位置、尿路梗阻程度及分侧肾功能，但已被CTU部分取代。E错误：MRI对钙化（结石）显示不敏感，一般不用于结石的初始诊断。</t>
   </si>
   <si>
+    <t>4 评分缺陷: 答案将KUB列为尿路结石诊断首选，与非增强CT的更高准确性及当前路径不符。</t>
+  </si>
+  <si>
+    <t>6 时效性缺陷: 当前急性疑结石评估不再以KUB作为首选确诊检查。</t>
+  </si>
+  <si>
     <t>为鉴别腹部X线平片上的钙化影是上尿路结石还是腹腔内钙化（如静脉石、淋巴结钙化），可采用的检查方法有：（AB）【不定项选择题，全部选对得2分，其余情况不得分】
 A. 拍摄腹部侧位X线平片
 B. 行泌尿系CT平扫
@@ -1368,6 +1596,9 @@
     <t>考点还原：尿路结石-上尿路结石
 参考答案：AB
 答案解析：正确答案是AB。A正确：拍摄侧位片有助于鉴别，因为尿路结石通常位于脊柱前缘（与脊柱重叠或在其前方），而腹腔内钙化（如静脉石、淋巴结钙化）多位于脊柱前方。B正确：CT平扫分辨率高，能清晰显示结石的精确位置、大小、成分以及与泌尿系解剖结构的关系，是鉴别诊断最可靠的方法。C、D、E（IVU、B超、逆行造影）也有助于判断钙化影是否在尿路内，但不如A、B直接和常用。</t>
+  </si>
+  <si>
+    <t>4 评分缺陷: 题干问“可采用”的检查，IVU和超声在特定场景亦可辅助定位；仅给AB使评分标准过窄。</t>
   </si>
 </sst>
 </file>
@@ -1380,10 +1611,17 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1533,7 +1771,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1543,6 +1781,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1859,16 +2103,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1877,37 +2118,37 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
@@ -1922,74 +2163,77 @@
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1999,11 +2243,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2316,14 +2572,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="45.070796460177" customWidth="1"/>
-    <col min="3" max="3" width="58.9469026548673" customWidth="1"/>
+    <col min="2" max="2" width="45.0727272727273" customWidth="1"/>
+    <col min="3" max="3" width="58.9454545454545" customWidth="1"/>
+    <col min="11" max="17" width="28.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:10">
+    <row r="1" customFormat="1" spans="1:17">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -2351,556 +2608,2077 @@
       <c r="J1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="152" customHeight="1" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="168" spans="1:17">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" ht="162" spans="1:10">
+      <c r="B2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" ht="168" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" ht="122.25" spans="1:10">
+      <c r="B3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" ht="126" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" ht="81" spans="1:10">
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" ht="98" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" ht="108" spans="1:10">
+      <c r="B5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" ht="112" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="94.5" spans="1:10">
+      <c r="B6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" ht="98" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" ht="94.5" spans="1:10">
+      <c r="B7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" ht="98" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="175.5" spans="1:10">
+      <c r="B8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="182" spans="1:17">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" ht="175.5" spans="1:10">
+      <c r="B9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" ht="182" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="135" spans="1:10">
+      <c r="B10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" ht="154" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" ht="148.5" spans="1:10">
+      <c r="B11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" ht="154" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" ht="121.5" spans="1:10">
+      <c r="B12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q12" s="7"/>
+    </row>
+    <row r="13" ht="126" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" ht="121.5" spans="1:10">
+      <c r="B13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+    </row>
+    <row r="14" ht="140" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" ht="121.5" spans="1:10">
+      <c r="B14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+    </row>
+    <row r="15" ht="126" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" ht="121.5" spans="1:10">
+      <c r="B15" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+    </row>
+    <row r="16" ht="126" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" ht="135" spans="1:3">
+      <c r="B16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+    </row>
+    <row r="17" ht="140" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" ht="121.5" spans="1:3">
+      <c r="B17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" ht="126" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="19" ht="121.5" spans="1:3">
+      <c r="B18" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" ht="126" spans="1:17">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" ht="108" spans="1:3">
+      <c r="B19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" ht="126" spans="1:17">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" ht="162" spans="1:3">
+      <c r="B20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" ht="168" spans="1:17">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" ht="121.5" spans="1:3">
+      <c r="B21" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" ht="140" spans="1:17">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" ht="175.5" spans="1:3">
+      <c r="B22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+    </row>
+    <row r="23" ht="182" spans="1:17">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" ht="108" spans="1:3">
+      <c r="B23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" ht="112" spans="1:17">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" ht="135" spans="1:3">
+      <c r="B24" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" ht="140" spans="1:17">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" ht="121.5" spans="1:3">
+      <c r="B25" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" ht="126" spans="1:17">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="189" spans="1:3">
+      <c r="B26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="196" spans="1:17">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" ht="189" spans="1:3">
+      <c r="B27" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" ht="210" spans="1:17">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" ht="189" spans="1:3">
+      <c r="B28" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7"/>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" ht="196" spans="1:17">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" ht="162" spans="1:3">
+      <c r="B29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q29" s="7"/>
+    </row>
+    <row r="30" ht="168" spans="1:17">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" ht="162" spans="1:3">
+      <c r="B30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q30" s="7"/>
+    </row>
+    <row r="31" ht="168" spans="1:17">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" ht="162" spans="1:3">
+      <c r="B31" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" ht="182" spans="1:17">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" ht="162" spans="1:3">
+      <c r="B32" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>1</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q32" s="7"/>
+    </row>
+    <row r="33" ht="168" spans="1:17">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" ht="162" spans="1:3">
+      <c r="B33" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" ht="168" spans="1:17">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" ht="162" spans="1:3">
+      <c r="B34" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" ht="168" spans="1:17">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" ht="121.5" spans="1:3">
+      <c r="B35" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+    </row>
+    <row r="36" ht="154" spans="1:17">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" ht="121.5" spans="1:3">
+      <c r="B36" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+    </row>
+    <row r="37" ht="126" spans="1:17">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" ht="148.5" spans="1:3">
+      <c r="B37" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+    </row>
+    <row r="38" ht="154" spans="1:17">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" ht="162" spans="1:3">
+      <c r="B38" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D38">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7"/>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+    </row>
+    <row r="39" ht="168" spans="1:17">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" ht="162" spans="1:3">
+      <c r="B39" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+    </row>
+    <row r="40" ht="168" spans="1:17">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="148.5" spans="1:3">
+      <c r="B40" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7"/>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="154" spans="1:17">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" ht="135" spans="1:3">
+      <c r="B41" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" ht="140" spans="1:17">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" ht="189" spans="1:3">
+      <c r="B42" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>1</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="L42" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+    </row>
+    <row r="43" ht="210" spans="1:17">
       <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="162" spans="1:3">
+      <c r="B43" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>1</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="L43" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="M43" s="7"/>
+      <c r="N43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="O43" s="7"/>
+      <c r="P43" s="7"/>
+      <c r="Q43" s="7"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="168" spans="1:17">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" ht="135" spans="1:3">
+      <c r="B44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" ht="154" spans="1:17">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" ht="94.5" spans="1:3">
+      <c r="B45" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+    </row>
+    <row r="46" ht="112" spans="1:17">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" ht="175.5" spans="1:3">
+      <c r="B46" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+    </row>
+    <row r="47" ht="182" spans="1:17">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" ht="135" spans="1:3">
+      <c r="B47" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>1</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+    </row>
+    <row r="48" ht="140" spans="1:17">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" ht="108" spans="1:3">
+      <c r="B48" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7"/>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7"/>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7"/>
+      <c r="Q48" s="7"/>
+    </row>
+    <row r="49" ht="112" spans="1:17">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" ht="121.5" spans="1:3">
+      <c r="B49" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+    </row>
+    <row r="50" ht="126" spans="1:17">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="51" ht="121.5" spans="1:3">
+      <c r="B50" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7"/>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7"/>
+      <c r="Q50" s="7"/>
+    </row>
+    <row r="51" ht="126" spans="1:17">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>101</v>
-      </c>
+      <c r="B51" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7"/>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2912,14 +4690,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Q51"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="2" max="2" width="45.070796460177" customWidth="1"/>
-    <col min="3" max="3" width="58.9469026548673" customWidth="1"/>
+    <col min="2" max="2" width="45.0727272727273" customWidth="1"/>
+    <col min="3" max="3" width="58.9454545454545" customWidth="1"/>
+    <col min="11" max="17" width="28.6363636363636" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:17">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -2947,556 +4726,2065 @@
       <c r="J1">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="121.5" spans="1:10">
+      <c r="K1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="140" spans="1:17">
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" ht="94.5" spans="1:10">
+      <c r="B2" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="5"/>
+      <c r="P2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q2" s="5"/>
+    </row>
+    <row r="3" ht="98" spans="1:17">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" ht="94.5" spans="1:10">
+      <c r="B3" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q3" s="7"/>
+    </row>
+    <row r="4" ht="98" spans="1:17">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" ht="94.5" spans="1:10">
+      <c r="B4" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q4" s="7"/>
+    </row>
+    <row r="5" ht="112" spans="1:17">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" ht="108" spans="1:10">
+      <c r="B5" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" ht="112" spans="1:17">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" ht="94.5" spans="1:10">
+      <c r="B6" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" ht="98" spans="1:17">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="8" ht="121.5" spans="1:10">
+      <c r="B7" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" ht="126" spans="1:17">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="121.5" spans="1:10">
+      <c r="B8" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="126" spans="1:17">
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="10" ht="148.5" spans="1:10">
+      <c r="B9" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="5"/>
+      <c r="L9" s="5"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
+    </row>
+    <row r="10" ht="168" spans="1:17">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="11" ht="121.5" spans="1:10">
+      <c r="B10" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" ht="126" spans="1:17">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" ht="121.5" spans="1:10">
+      <c r="B11" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" ht="126" spans="1:17">
       <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" ht="162" spans="1:10">
+      <c r="B12" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+    </row>
+    <row r="13" ht="168" spans="1:17">
       <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" ht="121.5" spans="1:10">
+      <c r="B13" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+    </row>
+    <row r="14" ht="126" spans="1:17">
       <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" ht="148.5" spans="1:10">
+      <c r="B14" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+    </row>
+    <row r="15" ht="154" spans="1:17">
       <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" ht="135" spans="1:10">
+      <c r="B15" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+    </row>
+    <row r="16" ht="140" spans="1:17">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="17" ht="121.5" spans="1:3">
+      <c r="B16" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+    </row>
+    <row r="17" ht="126" spans="1:17">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="18" ht="121.5" spans="1:3">
+      <c r="B17" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" ht="126" spans="1:17">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="19" ht="121.5" spans="1:3">
+      <c r="B18" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" ht="126" spans="1:17">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20" ht="121.5" spans="1:3">
+      <c r="B19" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" ht="126" spans="1:17">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" ht="121.5" spans="1:3">
+      <c r="B20" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7"/>
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" ht="126" spans="1:17">
       <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" ht="121.5" spans="1:3">
+      <c r="B21" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" ht="126" spans="1:17">
       <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="23" ht="121.5" spans="1:3">
+      <c r="B22" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7"/>
+      <c r="Q22" s="7"/>
+    </row>
+    <row r="23" ht="140" spans="1:17">
       <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="24" ht="121.5" spans="1:3">
+      <c r="B23" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>1</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" ht="126" spans="1:17">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="25" ht="108" spans="1:3">
+      <c r="B24" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" ht="112" spans="1:17">
       <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="26" ht="148.5" spans="1:3">
+      <c r="B25" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" ht="154" spans="1:17">
       <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="162" spans="1:3">
+      <c r="B26" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="182" spans="1:17">
       <c r="A27" s="1">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="28" ht="189.4" spans="1:3">
+      <c r="B27" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27" s="1">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+    </row>
+    <row r="28" ht="196" spans="1:17">
       <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" ht="175.9" spans="1:3">
+      <c r="B28" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>1</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" ht="182" spans="1:17">
       <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="30" ht="189.4" spans="1:3">
+      <c r="B29" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7"/>
+      <c r="Q29" s="7"/>
+    </row>
+    <row r="30" ht="196" spans="1:17">
       <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="31" ht="162" spans="1:3">
+      <c r="B30" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+      <c r="F30">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="7"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+    </row>
+    <row r="31" ht="168" spans="1:17">
       <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="32" ht="162" spans="1:3">
+      <c r="B31" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+      <c r="F31">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="7"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7"/>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" ht="168" spans="1:17">
       <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="33" ht="148.5" spans="1:3">
+      <c r="B32" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+    </row>
+    <row r="33" ht="154" spans="1:17">
       <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" ht="148.5" spans="1:3">
+      <c r="B33" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+      <c r="F33">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+    </row>
+    <row r="34" ht="154" spans="1:17">
       <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="35" ht="135" spans="1:3">
+      <c r="B34" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>1</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q34" s="7"/>
+    </row>
+    <row r="35" ht="154" spans="1:17">
       <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="36" ht="135" spans="1:3">
+      <c r="B35" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="7"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7"/>
+      <c r="Q35" s="7"/>
+    </row>
+    <row r="36" ht="140" spans="1:17">
       <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="37" ht="135" spans="1:3">
+      <c r="B36" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="7"/>
+      <c r="O36" s="7"/>
+      <c r="P36" s="7"/>
+      <c r="Q36" s="7"/>
+    </row>
+    <row r="37" ht="140" spans="1:17">
       <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" ht="148.5" spans="1:3">
+      <c r="B37" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>0</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="L37" s="7"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="7"/>
+      <c r="O37" s="7"/>
+      <c r="P37" s="7"/>
+      <c r="Q37" s="7"/>
+    </row>
+    <row r="38" ht="154" spans="1:17">
       <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" ht="135" spans="1:3">
+      <c r="B38" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>0</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="M38" s="7"/>
+      <c r="N38" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q38" s="7"/>
+    </row>
+    <row r="39" ht="140" spans="1:17">
       <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="40" ht="148.5" spans="1:3">
+      <c r="B39" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="7"/>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+    </row>
+    <row r="40" ht="154" spans="1:17">
       <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="108" spans="1:3">
+      <c r="B40" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+      <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
+        <v>1</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="M40" s="7"/>
+      <c r="N40" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q40" s="7"/>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="112" spans="1:17">
       <c r="A41" s="1">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="42" ht="121.5" spans="1:3">
+      <c r="B41" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="D41" s="1">
+        <v>0</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0</v>
+      </c>
+      <c r="F41" s="1">
+        <v>0</v>
+      </c>
+      <c r="G41" s="1">
+        <v>0</v>
+      </c>
+      <c r="H41" s="1">
+        <v>0</v>
+      </c>
+      <c r="I41" s="1">
+        <v>0</v>
+      </c>
+      <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+    </row>
+    <row r="42" ht="126" spans="1:17">
       <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="43" s="2" customFormat="1" ht="108" spans="1:3">
+      <c r="B42" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D42">
+        <v>0</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="7"/>
+      <c r="O42" s="7"/>
+      <c r="P42" s="7"/>
+      <c r="Q42" s="7"/>
+    </row>
+    <row r="43" s="2" customFormat="1" ht="112" spans="1:17">
       <c r="A43" s="2">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="108" spans="1:3">
+      <c r="B43" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="D43" s="2">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2">
+        <v>0</v>
+      </c>
+      <c r="F43" s="2">
+        <v>0</v>
+      </c>
+      <c r="G43" s="2">
+        <v>0</v>
+      </c>
+      <c r="H43" s="2">
+        <v>0</v>
+      </c>
+      <c r="I43" s="2">
+        <v>0</v>
+      </c>
+      <c r="J43" s="2">
+        <v>0</v>
+      </c>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="M43" s="8"/>
+      <c r="N43" s="8"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="8"/>
+      <c r="Q43" s="8"/>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="140" spans="1:17">
       <c r="A44" s="1">
         <v>43</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="45" ht="121.5" spans="1:3">
+      <c r="B44" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0</v>
+      </c>
+      <c r="F44" s="1">
+        <v>0</v>
+      </c>
+      <c r="G44" s="1">
+        <v>0</v>
+      </c>
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+    </row>
+    <row r="45" ht="126" spans="1:17">
       <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="46" ht="121.5" spans="1:3">
+      <c r="B45" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="7"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="7"/>
+      <c r="O45" s="7"/>
+      <c r="P45" s="7"/>
+      <c r="Q45" s="7"/>
+    </row>
+    <row r="46" ht="126" spans="1:17">
       <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="47" ht="108" spans="1:3">
+      <c r="B46" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46" s="7"/>
+      <c r="L46" s="7"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="7"/>
+      <c r="O46" s="7"/>
+      <c r="P46" s="7"/>
+      <c r="Q46" s="7"/>
+    </row>
+    <row r="47" ht="112" spans="1:17">
       <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="48" ht="162" spans="1:3">
+      <c r="B47" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" s="7"/>
+      <c r="L47" s="7"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="7"/>
+      <c r="O47" s="7"/>
+      <c r="P47" s="7"/>
+      <c r="Q47" s="7"/>
+    </row>
+    <row r="48" ht="168" spans="1:17">
       <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="49" ht="121.5" spans="1:3">
+      <c r="B48" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>1</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="L48" s="7"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="O48" s="7"/>
+      <c r="P48" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q48" s="7"/>
+    </row>
+    <row r="49" ht="126" spans="1:17">
       <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="50" ht="121.5" spans="1:3">
+      <c r="B49" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="7"/>
+      <c r="O49" s="7"/>
+      <c r="P49" s="7"/>
+      <c r="Q49" s="7"/>
+    </row>
+    <row r="50" ht="126" spans="1:17">
       <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="51" ht="121.5" spans="1:3">
+      <c r="B50" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>1</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="O50" s="7"/>
+      <c r="P50" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q50" s="7"/>
+    </row>
+    <row r="51" ht="126" spans="1:17">
       <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>201</v>
-      </c>
+      <c r="B51" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51" s="7"/>
+      <c r="L51" s="7"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="O51" s="7"/>
+      <c r="P51" s="7"/>
+      <c r="Q51" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3509,7 +6797,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
